--- a/結合テスト仕様書.xlsx
+++ b/結合テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="56">
   <si>
     <t>テスト区分</t>
   </si>
@@ -100,7 +100,12 @@
     <t>権限表示変換</t>
   </si>
   <si>
-    <t>「管理者」を選択して確認画面へ遷移</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録画面で値を入力する。
+⑤「管理者」を選択して確認画面へ遷移
+⑥画面下部にある「確認する」を押下</t>
   </si>
   <si>
     <t>確認画面に「管理者」と表示される</t>
@@ -113,7 +118,11 @@
     <t>戻る（入力保持）</t>
   </si>
   <si>
-    <t>確認画面で「前に戻る」押下</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録画面で値を入力する。
+⑤確認画面で「前に戻る」押下</t>
   </si>
   <si>
     <t>登録画面に戻り、入力値が保持されている</t>
@@ -126,7 +135,10 @@
     <t>再入力→再確認</t>
   </si>
   <si>
-    <t>戻った後に一部修正し「確認する」押下</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④戻った後に一部修正し「確認する」押下</t>
   </si>
   <si>
     <t>修正内容が確認画面に反映される</t>
@@ -139,9 +151,6 @@
     <t>DB登録</t>
   </si>
   <si>
-    <t>確認画面で「登録する」押下</t>
-  </si>
-  <si>
     <t>DBに入力値が正しく登録される</t>
   </si>
   <si>
@@ -152,9 +161,6 @@
     <t>完了画面遷移</t>
   </si>
   <si>
-    <t>登録処理完了後</t>
-  </si>
-  <si>
     <t>完了画面に遷移する</t>
   </si>
   <si>
@@ -165,7 +171,11 @@
     <t>DBエラー時の動作</t>
   </si>
   <si>
-    <t>DB接続を切断して登録実行</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録画面で値を入力する。
+⑤DB接続を切断して登録実行</t>
   </si>
   <si>
     <t>エラーメッセージが表示され登録されない</t>
@@ -200,49 +210,15 @@
     <t>セッション切れ</t>
   </si>
   <si>
-    <t>入力後、時間を空けて確認画面へ遷移</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録画面で値を入力する。
+⑤画面下部にある「確認する」を押下。
+⑥入力後、時間を空けて確認画面へ遷移</t>
   </si>
   <si>
     <t>入力情報が保持されない、またはエラー表示</t>
-  </si>
-  <si>
-    <t>結合観点
-結合テストの主目的</t>
-  </si>
-  <si>
-    <t>画面→画面データ連携</t>
-  </si>
-  <si>
-    <t>登録画面で入力→確認画面表示</t>
-  </si>
-  <si>
-    <t>全項目の値が正しく引き渡される</t>
-  </si>
-  <si>
-    <t>結合観点
-カラム対応確認</t>
-  </si>
-  <si>
-    <t>画面→DB連携</t>
-  </si>
-  <si>
-    <t>確認画面から登録実行</t>
-  </si>
-  <si>
-    <t>DBの各カラムに正しい値で登録される</t>
-  </si>
-  <si>
-    <t>結合観点
-セキュリティ重要項目</t>
-  </si>
-  <si>
-    <t>パスワードハッシュ化</t>
-  </si>
-  <si>
-    <t>登録処理実行</t>
-  </si>
-  <si>
-    <t>DBにハッシュ化された値が保存される</t>
   </si>
 </sst>
 </file>
@@ -309,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -333,6 +309,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -637,9 +616,15 @@
       <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="2"/>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="8">
+        <v>46106.0</v>
+      </c>
       <c r="I3" s="6"/>
       <c r="J3" s="7" t="s">
         <v>16</v>
@@ -661,9 +646,15 @@
       <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="2"/>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="8">
+        <v>46106.0</v>
+      </c>
       <c r="I4" s="6"/>
       <c r="J4" s="7" t="s">
         <v>16</v>
@@ -685,9 +676,15 @@
       <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="2"/>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="8">
+        <v>46107.0</v>
+      </c>
       <c r="I5" s="6"/>
       <c r="J5" s="7" t="s">
         <v>16</v>
@@ -709,9 +706,15 @@
       <c r="E6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="2"/>
+      <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="8">
+        <v>46108.0</v>
+      </c>
       <c r="I6" s="6"/>
       <c r="J6" s="7" t="s">
         <v>16</v>
@@ -733,9 +736,15 @@
       <c r="E7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="2"/>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="8">
+        <v>46109.0</v>
+      </c>
       <c r="I7" s="6"/>
       <c r="J7" s="7" t="s">
         <v>16</v>
@@ -752,14 +761,20 @@
         <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="2"/>
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="8">
+        <v>46110.0</v>
+      </c>
       <c r="I8" s="6"/>
       <c r="J8" s="7" t="s">
         <v>16</v>
@@ -767,23 +782,29 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2">
         <v>8.0</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="2"/>
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="8">
+        <v>46111.0</v>
+      </c>
       <c r="I9" s="6"/>
       <c r="J9" s="7" t="s">
         <v>16</v>
@@ -791,23 +812,29 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2">
         <v>9.0</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="2"/>
+      <c r="F10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="8">
+        <v>46112.0</v>
+      </c>
       <c r="I10" s="6"/>
       <c r="J10" s="7" t="s">
         <v>16</v>
@@ -815,23 +842,29 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2">
         <v>10.0</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="2"/>
+      <c r="F11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="8">
+        <v>46113.0</v>
+      </c>
       <c r="I11" s="6"/>
       <c r="J11" s="7" t="s">
         <v>16</v>
@@ -839,23 +872,29 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2">
         <v>11.0</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="2"/>
+      <c r="F12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="8">
+        <v>46114.0</v>
+      </c>
       <c r="I12" s="6"/>
       <c r="J12" s="7" t="s">
         <v>16</v>
@@ -863,103 +902,37 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2">
         <v>12.0</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="2"/>
+      <c r="F13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="8">
+        <v>46115.0</v>
+      </c>
       <c r="I13" s="6"/>
       <c r="J13" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F13">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/結合テスト仕様書.xlsx
+++ b/結合テスト仕様書.xlsx
@@ -285,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -302,16 +302,13 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -593,7 +590,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="5">
-        <v>46105.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="7" t="s">
@@ -622,8 +619,8 @@
       <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="8">
-        <v>46106.0</v>
+      <c r="H3" s="5">
+        <v>46112.0</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="7" t="s">
@@ -652,8 +649,8 @@
       <c r="G4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="8">
-        <v>46106.0</v>
+      <c r="H4" s="5">
+        <v>46112.0</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="7" t="s">
@@ -682,8 +679,8 @@
       <c r="G5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="8">
-        <v>46107.0</v>
+      <c r="H5" s="5">
+        <v>46112.0</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="7" t="s">
@@ -712,8 +709,8 @@
       <c r="G6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="8">
-        <v>46108.0</v>
+      <c r="H6" s="5">
+        <v>46112.0</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="7" t="s">
@@ -742,8 +739,8 @@
       <c r="G7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="8">
-        <v>46109.0</v>
+      <c r="H7" s="5">
+        <v>46112.0</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="7" t="s">
@@ -772,8 +769,8 @@
       <c r="G8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="8">
-        <v>46110.0</v>
+      <c r="H8" s="5">
+        <v>46112.0</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="7" t="s">
@@ -802,8 +799,8 @@
       <c r="G9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="8">
-        <v>46111.0</v>
+      <c r="H9" s="5">
+        <v>46112.0</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="7" t="s">
@@ -832,7 +829,7 @@
       <c r="G10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="5">
         <v>46112.0</v>
       </c>
       <c r="I10" s="6"/>
@@ -862,8 +859,8 @@
       <c r="G11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="8">
-        <v>46113.0</v>
+      <c r="H11" s="5">
+        <v>46112.0</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="7" t="s">
@@ -892,8 +889,8 @@
       <c r="G12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="8">
-        <v>46114.0</v>
+      <c r="H12" s="5">
+        <v>46112.0</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="7" t="s">
@@ -922,8 +919,8 @@
       <c r="G13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="8">
-        <v>46115.0</v>
+      <c r="H13" s="5">
+        <v>46112.0</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="7" t="s">
